--- a/2018/Mount4/Mount4_members_final.xlsx
+++ b/2018/Mount4/Mount4_members_final.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب سبعة</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
